--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9BF9BD-16A7-4E44-AD5D-20C1C584DC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95530359-8A25-4764-9A80-143E193FA604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$12:$D$118</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="114">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -114,9 +117,6 @@
     <t>Zohra Mart</t>
   </si>
   <si>
-    <t>Sohail Traders</t>
-  </si>
-  <si>
     <t xml:space="preserve">Clinix </t>
   </si>
   <si>
@@ -174,9 +174,6 @@
     <t xml:space="preserve">Risen Gajumata </t>
   </si>
   <si>
-    <t>Nabeel Traders</t>
-  </si>
-  <si>
     <t xml:space="preserve">Goutmet MIX </t>
   </si>
   <si>
@@ -211,6 +208,168 @@
   </si>
   <si>
     <t>Sweera GT Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zubaida Traders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food </t>
+  </si>
+  <si>
+    <t>Raheem Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lutaf Mart </t>
+  </si>
+  <si>
+    <t>Vip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Rehmat </t>
+  </si>
+  <si>
+    <t>Clinic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jala Sons Behria </t>
+  </si>
+  <si>
+    <t>Jalal Sons Izmir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow C NC </t>
+  </si>
+  <si>
+    <t>Jalal Sons Behria Orchard</t>
+  </si>
+  <si>
+    <t>Rainbow CNC DHA</t>
+  </si>
+  <si>
+    <t>LGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI Mart Jore Pull </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Manawan </t>
+  </si>
+  <si>
+    <t>Rainbow Sheikhupura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pak Madina </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Askari Punjab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Shadbagh </t>
+  </si>
+  <si>
+    <t>Risen Sabzazaar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Thoker </t>
+  </si>
+  <si>
+    <t>Risen Askari 11</t>
+  </si>
+  <si>
+    <t>Gourmet Food</t>
+  </si>
+  <si>
+    <t>Clinix Werehouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem Wapda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cario Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Fateh Gher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zohra Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Johar Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food 12G Johar Town </t>
+  </si>
+  <si>
+    <t>Gourmet Food Naseer Abad</t>
+  </si>
+  <si>
+    <t>Gourmet Food Multan Road Fwara Chowk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Faisal Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food 18G Iqbal Town </t>
+  </si>
+  <si>
+    <t>Gourmet Food Samnabad Lhr</t>
+  </si>
+  <si>
+    <t>Gourmet Food Ghalib Market</t>
+  </si>
+  <si>
+    <t>Gourmet Food Islam Pura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Jinnah Hospital </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Shama Cenima </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Muslim Town Ayubia </t>
+  </si>
+  <si>
+    <t>Gourmet Food Walton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food C Block Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Liyaqat Chowk </t>
+  </si>
+  <si>
+    <t>Gourmet Food Krishan Nagar</t>
+  </si>
+  <si>
+    <t>Gourmet Food Poonch Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Nadeem Shaheed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Gulshan Ravi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Link Road Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Jauray Pull </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Bhatta Chowk </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food EME Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food  DHA XX- Block </t>
   </si>
 </sst>
 </file>
@@ -318,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -367,6 +526,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -683,12 +845,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DC3771-1E8D-4C4A-A561-EB9042DCC7D5}">
-  <dimension ref="A1:AN76"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AN118"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="8.7265625" customWidth="1"/>
     <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="1.90625" bestFit="1" customWidth="1"/>
@@ -781,7 +946,7 @@
         <v>46257</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -1985,7 +2150,7 @@
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1999,7 +2164,7 @@
       <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -2013,7 +2178,7 @@
       <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>35</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2027,7 +2192,7 @@
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2">
         <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -2041,7 +2206,7 @@
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>48</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -2055,7 +2220,7 @@
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2">
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -2069,7 +2234,7 @@
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="2">
         <v>9</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -2078,13 +2243,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="1">
-        <v>100</v>
+      <c r="C21" s="2">
+        <v>35</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>22</v>
@@ -2097,8 +2262,8 @@
       <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="1">
-        <v>35</v>
+      <c r="C22" s="2">
+        <v>16.5</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>22</v>
@@ -2106,13 +2271,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="1">
-        <v>16.5</v>
+      <c r="C23" s="2">
+        <v>21.3</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>22</v>
@@ -2125,8 +2290,8 @@
       <c r="B24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="1">
-        <v>21.3</v>
+      <c r="C24" s="2">
+        <v>6.55</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>22</v>
@@ -2139,8 +2304,8 @@
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="1">
-        <v>6.55</v>
+      <c r="C25" s="2">
+        <v>21.975000000000001</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>22</v>
@@ -2153,8 +2318,8 @@
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="1">
-        <v>21.975000000000001</v>
+      <c r="C26" s="2">
+        <v>13</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>22</v>
@@ -2167,8 +2332,8 @@
       <c r="B27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="1">
-        <v>13</v>
+      <c r="C27" s="2">
+        <v>15</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>22</v>
@@ -2181,8 +2346,8 @@
       <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="1">
-        <v>15</v>
+      <c r="C28" s="2">
+        <v>190</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>22</v>
@@ -2190,13 +2355,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="1">
-        <v>190</v>
+      <c r="C29" s="2">
+        <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>22</v>
@@ -2209,8 +2374,8 @@
       <c r="B30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="1">
-        <v>15</v>
+      <c r="C30" s="2">
+        <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>22</v>
@@ -2223,8 +2388,8 @@
       <c r="B31" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="1">
-        <v>27</v>
+      <c r="C31" s="2">
+        <v>10</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>22</v>
@@ -2237,8 +2402,8 @@
       <c r="B32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="1">
-        <v>10</v>
+      <c r="C32" s="2">
+        <v>17</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>22</v>
@@ -2251,8 +2416,8 @@
       <c r="B33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="1">
-        <v>17</v>
+      <c r="C33" s="2">
+        <v>9</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>22</v>
@@ -2260,13 +2425,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="1">
-        <v>9</v>
+        <v>21</v>
+      </c>
+      <c r="C34" s="2">
+        <v>7</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>22</v>
@@ -2277,10 +2442,10 @@
         <v>46245</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="1">
-        <v>7</v>
+        <v>43</v>
+      </c>
+      <c r="C35" s="2">
+        <v>14</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>22</v>
@@ -2288,13 +2453,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="1">
-        <v>14</v>
+      <c r="C36" s="2">
+        <v>5.5</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>22</v>
@@ -2307,8 +2472,8 @@
       <c r="B37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="1">
-        <v>5.5</v>
+      <c r="C37" s="2">
+        <v>30</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>22</v>
@@ -2321,8 +2486,8 @@
       <c r="B38" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="1">
-        <v>30</v>
+      <c r="C38" s="2">
+        <v>6</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>22</v>
@@ -2335,8 +2500,8 @@
       <c r="B39" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="1">
-        <v>6</v>
+      <c r="C39" s="2">
+        <v>16</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>22</v>
@@ -2347,10 +2512,10 @@
         <v>46246</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="1">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="C40" s="2">
+        <v>17</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>22</v>
@@ -2360,11 +2525,11 @@
       <c r="A41" s="7">
         <v>46246</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="1">
-        <v>17</v>
+      <c r="B41" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="2">
+        <v>60</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>22</v>
@@ -2372,13 +2537,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="1">
-        <v>450</v>
+      <c r="C42" s="2">
+        <v>10</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>22</v>
@@ -2386,13 +2551,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
-        <v>46246</v>
-      </c>
-      <c r="B43" s="15" t="s">
+        <v>46247</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="1">
-        <v>60</v>
+      <c r="C43" s="2">
+        <v>7</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>22</v>
@@ -2405,8 +2570,8 @@
       <c r="B44" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="1">
-        <v>10</v>
+      <c r="C44" s="2">
+        <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>22</v>
@@ -2414,13 +2579,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="1">
-        <v>7</v>
+      <c r="C45" s="2">
+        <v>5</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>22</v>
@@ -2428,13 +2593,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="1">
-        <v>6</v>
+      <c r="C46" s="2">
+        <v>12.975</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>22</v>
@@ -2447,8 +2612,8 @@
       <c r="B47" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="1">
-        <v>5</v>
+      <c r="C47" s="2">
+        <v>23</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>22</v>
@@ -2456,13 +2621,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="1">
-        <v>12.975</v>
+        <v>51</v>
+      </c>
+      <c r="C48" s="2">
+        <v>6</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>22</v>
@@ -2470,13 +2635,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="1">
-        <v>23</v>
+        <v>55</v>
+      </c>
+      <c r="C49" s="2">
+        <v>4.9749999999999996</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>22</v>
@@ -2484,13 +2649,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="1">
-        <v>6</v>
+        <v>56</v>
+      </c>
+      <c r="C50" s="2">
+        <v>10.199999999999999</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>22</v>
@@ -2503,8 +2668,8 @@
       <c r="B51" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="1">
-        <v>4.9749999999999996</v>
+      <c r="C51" s="2">
+        <v>15</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>22</v>
@@ -2517,8 +2682,8 @@
       <c r="B52" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="1">
-        <v>10.199999999999999</v>
+      <c r="C52" s="2">
+        <v>12</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>22</v>
@@ -2531,8 +2696,8 @@
       <c r="B53" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="1">
-        <v>15</v>
+      <c r="C53" s="2">
+        <v>30</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>22</v>
@@ -2540,13 +2705,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="1">
-        <v>12</v>
+        <v>51</v>
+      </c>
+      <c r="C54" s="2">
+        <v>89.65</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>22</v>
@@ -2554,148 +2719,896 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" s="2">
+        <v>125</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C56" s="2">
+        <v>32.975000000000001</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="2">
+        <v>9</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="2">
+        <v>15</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" s="2">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="2">
         <v>30</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
+      <c r="D60" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
+      <c r="A61" s="7">
+        <v>46255</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="2">
+        <v>7.05</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+      <c r="A62" s="7">
+        <v>46255</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="2">
+        <v>44</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
+      <c r="A63" s="7">
+        <v>46255</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="2">
+        <v>9</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
+      <c r="A64" s="7">
+        <v>46255</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="2">
+        <v>4</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
+      <c r="A65" s="7">
+        <v>46255</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="2">
+        <v>2</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
+      <c r="A66" s="7">
+        <v>46255</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="2">
+        <v>22</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
+      <c r="A67" s="7">
+        <v>46256</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="2">
+        <v>14</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
+      <c r="A68" s="7">
+        <v>46256</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="2">
+        <v>11</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
+      <c r="A69" s="7">
+        <v>46256</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="2">
+        <v>14</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
+      <c r="A70" s="7">
+        <v>46258</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C70" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
+      <c r="A71" s="7">
+        <v>46258</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" s="2">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
+      <c r="A72" s="7">
+        <v>46258</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="2">
+        <v>3.9750000000000001</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
+      <c r="A73" s="7">
+        <v>46258</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="2">
+        <v>4</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
+      <c r="A74" s="7">
+        <v>46258</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="2">
+        <v>13</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
+      <c r="A75" s="7">
+        <v>46259</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C75" s="2">
+        <v>4</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="7">
+        <v>46259</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" s="2">
+        <v>4</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="7">
+        <v>46259</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="2">
+        <v>6</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="7">
+        <v>46259</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C78" s="2">
+        <v>5</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="7">
+        <v>46259</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C79" s="2">
+        <v>13</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="7">
+        <v>46259</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C80" s="2">
+        <v>13</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C81" s="2">
+        <v>18</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C82" s="2">
+        <v>19.95</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C83" s="2">
+        <v>13</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" s="2">
+        <v>11</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C85" s="2">
+        <v>5.9749999999999996</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C86" s="2">
+        <v>6.9749999999999996</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C87" s="2">
+        <v>140</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="7">
+        <v>46262</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C88" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" s="7">
+        <v>46262</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C89" s="2">
+        <v>18</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" s="7">
+        <v>46263</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C90" s="2">
+        <v>26</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C91" s="2">
+        <v>12</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C92" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C93" s="2">
+        <v>5</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C94" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" s="2">
+        <v>1</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C96" s="2">
+        <v>30</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C97" s="2">
+        <v>1</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C98" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C100" s="2">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C101" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C102" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C103" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C105" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C106" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C107" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C108" s="2">
+        <v>1</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C110" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C111" s="2">
+        <v>2</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C112" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C113" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C115" s="2">
+        <v>1</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C116" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="7"/>
+      <c r="B118" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B76" s="1"/>
-      <c r="C76" s="4">
-        <f>SUM(C14:C75)</f>
-        <v>1387.9749999999999</v>
-      </c>
-      <c r="D76" s="1"/>
+      <c r="C118" s="10">
+        <f>SUM(C14:C117)</f>
+        <v>1737.2749999999996</v>
+      </c>
+      <c r="D118" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2703,6 +3616,6 @@
     <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="44" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>